--- a/outputs/tables/portfolio_annual_returns_all_methods_with_costs_taxes.xlsx
+++ b/outputs/tables/portfolio_annual_returns_all_methods_with_costs_taxes.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,279 +417,279 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MST_method1_degree_weighted</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MST_method1_market_cap_same_X</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MST_method2_degree_weighted</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MST_method2_market_cap_same_X</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>MST_method3_degree_weighted</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MST_method3_market_cap_same_X</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MST_method4_degree_weighted</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MST_method4_market_cap_same_X</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Top_market_cap_weighted</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>2018</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1166527543808488</v>
+        <v>-0.1166527543808482</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05881097468600238</v>
+        <v>-0.05881097468600216</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1033820894337535</v>
+        <v>-0.103382089433751</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.04460892488935397</v>
+        <v>-0.04460892488935209</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0927482304361259</v>
+        <v>-0.09274823043612657</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0542173005873775</v>
+        <v>-0.05421730058737939</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09598978932039093</v>
+        <v>-0.09598978932038849</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0482453844547891</v>
+        <v>-0.04824538445478987</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2291437487523263</v>
+        <v>-0.2291437487523268</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2019</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3262181329465226</v>
+        <v>0.3262181329465241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.326209905445884</v>
+        <v>0.3262099054458847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3721574348141252</v>
+        <v>0.372157434814125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3405630470835459</v>
+        <v>0.3405630470835463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.49220136880029</v>
+        <v>0.4922013688002922</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3475451755037393</v>
+        <v>0.3475451755037389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3069985232620285</v>
+        <v>0.3069985232620267</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3182091763264707</v>
+        <v>0.3182091763264683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2653204315125857</v>
+        <v>0.2653204315125837</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2020</v>
       </c>
       <c r="B4" t="n">
         <v>-0.01800774396033966</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0129858515512048</v>
+        <v>-0.01298585155120491</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05413799617585702</v>
+        <v>-0.05413799617585846</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02951872847632386</v>
+        <v>-0.02951872847632242</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07660947604720314</v>
+        <v>-0.07660947604720403</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1177690970688536</v>
+        <v>-0.1177690970688535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009683830375932789</v>
+        <v>0.009683830375930569</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01121125869666439</v>
+        <v>-0.01121125869666806</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.08970824753722562</v>
+        <v>-0.08970824753722506</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2021</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3187182859749533</v>
+        <v>0.3187182859749571</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2074078506514367</v>
+        <v>0.2074078506514385</v>
       </c>
       <c r="D5" t="n">
         <v>0.3022584660058159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1821684300568382</v>
+        <v>0.1821684300568367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.280871067863337</v>
+        <v>0.2808710678633364</v>
       </c>
       <c r="G5" t="n">
-        <v>0.184067582446483</v>
+        <v>0.1840675824464841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2866316782591332</v>
+        <v>0.2866316782591334</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2096360750132678</v>
+        <v>0.2096360750132684</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1824820441028756</v>
+        <v>0.1824820441028729</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2022</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.08204870478193504</v>
+        <v>-0.08204870478193405</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1077534408169223</v>
+        <v>-0.1077534408169216</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0747077459266261</v>
+        <v>-0.07470774592662643</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07669086232655786</v>
+        <v>-0.07669086232655864</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07852825292513266</v>
+        <v>-0.07852825292513299</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06752318231594834</v>
+        <v>-0.06752318231594756</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08376731161196838</v>
+        <v>-0.08376731161196804</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09026235241548763</v>
+        <v>-0.09026235241548686</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1271763175660156</v>
+        <v>-0.1271763175660163</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2278112797300922</v>
+        <v>0.227811279730092</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2881691626618075</v>
+        <v>0.2881691626618055</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2534152686800195</v>
+        <v>0.2534152686800175</v>
       </c>
       <c r="E7" t="n">
         <v>0.3108783237928567</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2378592288838197</v>
+        <v>0.2378592288838195</v>
       </c>
       <c r="G7" t="n">
         <v>0.2859969371327151</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2470702831329787</v>
+        <v>0.2470702831329779</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3155195922254341</v>
+        <v>0.3155195922254321</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3579310315943207</v>
+        <v>0.3579310315943229</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2024</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2004084385116252</v>
+        <v>0.2004084385116267</v>
       </c>
       <c r="C8" t="n">
-        <v>0.116196417700227</v>
+        <v>0.1161964177002255</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2188103811454216</v>
+        <v>0.2188103811454238</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2561298832907362</v>
+        <v>0.2561298832907377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2854299331891545</v>
+        <v>0.2854299331891543</v>
       </c>
       <c r="G8" t="n">
         <v>0.3362365091570685</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1853857630672469</v>
+        <v>0.1853857630672464</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09050979285157412</v>
+        <v>0.09050979285157346</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1298566311361466</v>
+        <v>0.1298566311361484</v>
       </c>
     </row>
   </sheetData>
